--- a/db/tabla_minable.xlsx
+++ b/db/tabla_minable.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PosGrado\Proyecto Titulacion\Timetabling\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PosGrado\Proyecto Titulacion\Timetabling\db\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{100808CB-CEDA-46E8-B6E7-88E2D5AF70A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAA8BC4C-099E-4AB6-8D90-71826D66292C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4320" yWindow="5040" windowWidth="28785" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="600" yWindow="2790" windowWidth="28785" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/db/tabla_minable.xlsx
+++ b/db/tabla_minable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PosGrado\Proyecto Titulacion\Timetabling\db\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAA8BC4C-099E-4AB6-8D90-71826D66292C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F802BA3E-9177-40C5-9CF5-A228E9BFD5CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="600" yWindow="2790" windowWidth="28785" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1017,6 +1017,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T151"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="9" max="9" width="16" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">

--- a/db/tabla_minable.xlsx
+++ b/db/tabla_minable.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PosGrado\Proyecto Titulacion\Timetabling\db\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F802BA3E-9177-40C5-9CF5-A228E9BFD5CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B41A8963-E148-4281-A0CE-6DED3A585189}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1018,6 +1018,7 @@
   <dimension ref="A1:T151"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="9.140625" customWidth="1"/>
     <col min="9" max="9" width="16" customWidth="1"/>
   </cols>
   <sheetData>
